--- a/data/heating_system_data.xlsx
+++ b/data/heating_system_data.xlsx
@@ -1053,7 +1053,7 @@
         <v>18</v>
       </c>
       <c r="Q6" s="1">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="R6" s="1">
         <v>0</v>

--- a/data/heating_system_data.xlsx
+++ b/data/heating_system_data.xlsx
@@ -910,7 +910,7 @@
         <v>0.02</v>
       </c>
       <c r="N4" s="1">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="O4" t="s">
         <v>17</v>

--- a/data/heating_system_data.xlsx
+++ b/data/heating_system_data.xlsx
@@ -747,13 +747,13 @@
         <v>7</v>
       </c>
       <c r="C2" s="3">
-        <v>1500</v>
+        <v>2288</v>
       </c>
       <c r="D2" s="3">
-        <v>2250</v>
+        <v>2847</v>
       </c>
       <c r="E2" s="3">
-        <v>3000</v>
+        <v>3406</v>
       </c>
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
@@ -767,10 +767,10 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>203</v>
       </c>
       <c r="L2">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="M2" s="1">
         <v>0.02</v>
@@ -785,7 +785,7 @@
         <v>18</v>
       </c>
       <c r="Q2" s="1">
-        <v>0.99</v>
+        <v>0.94</v>
       </c>
       <c r="R2" s="1">
         <v>0</v>
@@ -814,13 +814,13 @@
         <v>8</v>
       </c>
       <c r="C3" s="3">
-        <v>1500</v>
+        <v>2288</v>
       </c>
       <c r="D3" s="3">
-        <v>2250</v>
+        <v>2847</v>
       </c>
       <c r="E3" s="3">
-        <v>3000</v>
+        <v>3406</v>
       </c>
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
@@ -834,10 +834,10 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>203</v>
       </c>
       <c r="L3">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="M3" s="1">
         <v>0.02</v>
@@ -852,7 +852,7 @@
         <v>18</v>
       </c>
       <c r="Q3" s="1">
-        <v>0.99</v>
+        <v>0.94</v>
       </c>
       <c r="R3" s="1">
         <v>0</v>
@@ -881,13 +881,13 @@
         <v>11</v>
       </c>
       <c r="C4" s="3">
-        <v>5000</v>
+        <v>7843</v>
       </c>
       <c r="D4" s="3">
-        <v>6000</v>
+        <v>10160</v>
       </c>
       <c r="E4" s="3">
-        <v>7000</v>
+        <v>12476</v>
       </c>
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
@@ -898,10 +898,10 @@
         <v>67</v>
       </c>
       <c r="J4" s="3">
-        <v>5000</v>
+        <v>3063</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="L4">
         <v>15</v>
@@ -919,10 +919,10 @@
         <v>16</v>
       </c>
       <c r="Q4" s="1">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="R4" s="1">
-        <v>0.99</v>
+        <v>0.94</v>
       </c>
       <c r="S4">
         <v>0.8</v>
@@ -948,13 +948,13 @@
         <v>9</v>
       </c>
       <c r="C5" s="3">
-        <v>7500</v>
+        <v>12633</v>
       </c>
       <c r="D5" s="3">
-        <v>9000</v>
+        <v>15522</v>
       </c>
       <c r="E5" s="3">
-        <v>12000</v>
+        <v>18411</v>
       </c>
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
@@ -965,10 +965,10 @@
         <v>68</v>
       </c>
       <c r="J5" s="3">
-        <v>5000</v>
+        <v>3063</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="L5">
         <v>15</v>
@@ -986,7 +986,7 @@
         <v>18</v>
       </c>
       <c r="Q5" s="1">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="R5" s="1">
         <v>0</v>
